--- a/artfynd/A 47294-2023 artfynd.xlsx
+++ b/artfynd/A 47294-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130965937</v>
+        <v>130965934</v>
       </c>
       <c r="B2" t="n">
-        <v>98935</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496906</v>
+        <v>496972</v>
       </c>
       <c r="R2" t="n">
-        <v>6713334</v>
+        <v>6713641</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Måttliga förekomster . inventering åt vasa vind</t>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,39 +770,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+          <t>Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130965950</v>
+        <v>130965935</v>
       </c>
       <c r="B3" t="n">
-        <v>98935</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496938</v>
+        <v>496969</v>
       </c>
       <c r="R3" t="n">
-        <v>6713657</v>
+        <v>6713674</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,39 +872,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+          <t>Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130965952</v>
+        <v>130965941</v>
       </c>
       <c r="B4" t="n">
-        <v>98935</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496897</v>
+        <v>496960</v>
       </c>
       <c r="R4" t="n">
-        <v>6713695</v>
+        <v>6713554</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sparsamma förekomster . inventering åt vasa vind</t>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130965940</v>
+        <v>130965946</v>
       </c>
       <c r="B5" t="n">
-        <v>98935</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496969</v>
+        <v>496962</v>
       </c>
       <c r="R5" t="n">
-        <v>6713529</v>
+        <v>6713603</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130965930</v>
+        <v>130965949</v>
       </c>
       <c r="B6" t="n">
-        <v>98935</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496938</v>
+        <v>496950</v>
       </c>
       <c r="R6" t="n">
-        <v>6713359</v>
+        <v>6713633</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Måttlig förekomst . inventering åt vasa vind</t>
+          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,17 +1178,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130965938</v>
+        <v>130965859</v>
       </c>
       <c r="B7" t="n">
-        <v>98935</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496967</v>
+        <v>497079</v>
       </c>
       <c r="R7" t="n">
-        <v>6713476</v>
+        <v>6713662</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sparsam förekomst . inventering åt vasa vind</t>
+          <t>Födosökspår . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+          <t>Anders Esplund, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130965931</v>
+        <v>130965860</v>
       </c>
       <c r="B8" t="n">
-        <v>98935</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496973</v>
+        <v>497061</v>
       </c>
       <c r="R8" t="n">
-        <v>6713428</v>
+        <v>6713661</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Måttliga förekomster . inventering åt vasa vind</t>
+          <t>Spillning . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,17 +1382,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning</t>
+          <t>Anders Esplund, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130965953</v>
+        <v>130965862</v>
       </c>
       <c r="B9" t="n">
-        <v>98935</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496924</v>
+        <v>497156</v>
       </c>
       <c r="R9" t="n">
-        <v>6713778</v>
+        <v>6713434</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Måttliga förekomster . inventering åt vasa vind</t>
+          <t>Spillning . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+          <t>Anders Esplund, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130965848</v>
+        <v>130965933</v>
       </c>
       <c r="B10" t="n">
-        <v>98935</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497082</v>
+        <v>496972</v>
       </c>
       <c r="R10" t="n">
-        <v>6713643</v>
+        <v>6713641</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttlig förekomst . inventering åt vasa vind</t>
+          <t>Spillning . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130965861</v>
+        <v>130965939</v>
       </c>
       <c r="B11" t="n">
-        <v>98935</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497138</v>
+        <v>496958</v>
       </c>
       <c r="R11" t="n">
-        <v>6713448</v>
+        <v>6713517</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+          <t>Spillning . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,39 +1688,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Esplund, Pia Edfors, Enviro Planning</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130965935</v>
+        <v>130965838</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496969</v>
+        <v>496949</v>
       </c>
       <c r="R12" t="n">
-        <v>6713674</v>
+        <v>6713860</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130965951</v>
+        <v>130965841</v>
       </c>
       <c r="B13" t="n">
-        <v>98935</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496906</v>
+        <v>497195</v>
       </c>
       <c r="R13" t="n">
-        <v>6713683</v>
+        <v>6713656</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+          <t>Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130965932</v>
+        <v>130965847</v>
       </c>
       <c r="B14" t="n">
-        <v>98935</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496961</v>
+        <v>497094</v>
       </c>
       <c r="R14" t="n">
-        <v>6713482</v>
+        <v>6713669</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1998,6 +1998,1536 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130965848</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497082</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6713643</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130965857</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497070</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6713694</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130965861</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>497138</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6713448</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130965873</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>497072</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6713161</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sparsam förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130965930</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496938</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6713359</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130965931</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496973</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6713428</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130965932</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496961</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6713482</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130965937</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496906</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6713334</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130965938</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496967</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6713476</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sparsam förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130965940</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496969</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6713529</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130965942</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496967</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6713571</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130965950</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496938</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6713657</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130965951</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496906</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6713683</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Betydelsefulla förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130965952</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>496897</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6713695</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Sparsamma förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130965953</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hissberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>496924</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6713778</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47294-2023 artfynd.xlsx
+++ b/artfynd/A 47294-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965934</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965935</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965941</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965946</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965949</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965859</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965860</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965862</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965933</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965939</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965838</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965841</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965847</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965848</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965857</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965861</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965873</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965930</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965931</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965932</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965937</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965938</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965940</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965942</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965950</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965951</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965952</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3528,8 +3668,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130965953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>